--- a/exports/trend_1d/SBICARD_full_report.xlsx
+++ b/exports/trend_1d/SBICARD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.22</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43930</v>
+        <v>43934</v>
       </c>
       <c r="H2" t="n">
-        <v>595.2</v>
+        <v>505.5</v>
       </c>
       <c r="I2" t="n">
         <v>554.6666585448141</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="K2" t="n">
-        <v>88.92</v>
+        <v>60.45</v>
       </c>
       <c r="L2" t="n">
         <v>2.21</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U2" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>37.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H3" t="n">
-        <v>570.05</v>
+        <v>611.3</v>
       </c>
       <c r="I3" t="n">
         <v>579.4030970641841</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.77</v>
+        <v>-20.93</v>
       </c>
       <c r="L3" t="n">
-        <v>19.66</v>
+        <v>23.84</v>
       </c>
       <c r="M3" t="n">
         <v>4.95</v>
       </c>
       <c r="N3" t="n">
-        <v>5.44</v>
+        <v>7.24</v>
       </c>
       <c r="O3" t="n">
         <v>-15.07</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>14.48</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44126</v>
+        <v>44127</v>
       </c>
       <c r="H4" t="n">
-        <v>851.9</v>
+        <v>807.25</v>
       </c>
       <c r="I4" t="n">
         <v>837.2137613708351</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K4" t="n">
-        <v>39.36</v>
+        <v>32.05</v>
       </c>
       <c r="L4" t="n">
         <v>9.619999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>6.52</v>
+        <v>7.27</v>
       </c>
       <c r="N4" t="n">
-        <v>4.85</v>
+        <v>5.24</v>
       </c>
       <c r="O4" t="n">
         <v>7.24</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>11.4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44168</v>
+        <v>44169</v>
       </c>
       <c r="H5" t="n">
-        <v>838.65</v>
+        <v>858.85</v>
       </c>
       <c r="I5" t="n">
         <v>857.6206408890685</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.89</v>
+        <v>-6.39</v>
       </c>
       <c r="L5" t="n">
         <v>7.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="N5" t="n">
         <v>5.23</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.58</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H6" t="n">
-        <v>1022.1</v>
+        <v>978.3</v>
       </c>
       <c r="I6" t="n">
         <v>984.1497101151963</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K6" t="n">
-        <v>19.01</v>
+        <v>13.91</v>
       </c>
       <c r="L6" t="n">
         <v>6.97</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>12.8</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H7" t="n">
-        <v>1011.85</v>
+        <v>1035.3</v>
       </c>
       <c r="I7" t="n">
         <v>1012.458628783263</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.43</v>
+        <v>-5.83</v>
       </c>
       <c r="L7" t="n">
-        <v>4.06</v>
+        <v>7.03</v>
       </c>
       <c r="M7" t="n">
         <v>2.82</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H8" t="n">
-        <v>1051.7</v>
+        <v>1005.9</v>
       </c>
       <c r="I8" t="n">
         <v>1011.689194709795</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>1.58</v>
+        <v>-2.84</v>
       </c>
       <c r="L8" t="n">
-        <v>2.33</v>
+        <v>5.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19</v>
+        <v>3.87</v>
       </c>
       <c r="N8" t="n">
         <v>4.94</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44406</v>
+        <v>44407</v>
       </c>
       <c r="H9" t="n">
-        <v>1017.45</v>
+        <v>1036.75</v>
       </c>
       <c r="I9" t="n">
         <v>1026.192866474708</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.15</v>
+        <v>-3.07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>3.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.37</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44462</v>
+        <v>44463</v>
       </c>
       <c r="H10" t="n">
-        <v>1049</v>
+        <v>1011.2</v>
       </c>
       <c r="I10" t="n">
         <v>1029.350740788659</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>1.18</v>
+        <v>-2.46</v>
       </c>
       <c r="L10" t="n">
         <v>4.03</v>
@@ -1011,7 +1130,7 @@
         <v>3.86</v>
       </c>
       <c r="N10" t="n">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.9</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.04</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44475</v>
+        <v>44476</v>
       </c>
       <c r="H11" t="n">
-        <v>1098.15</v>
+        <v>1139.35</v>
       </c>
       <c r="I11" t="n">
         <v>1115.925261518602</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.6</v>
+        <v>-12.67</v>
       </c>
       <c r="L11" t="n">
-        <v>10.14</v>
+        <v>13.02</v>
       </c>
       <c r="M11" t="n">
-        <v>0.87</v>
+        <v>2.57</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
         <v>-3.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H12" t="n">
-        <v>1061.9</v>
+        <v>1028.95</v>
       </c>
       <c r="I12" t="n">
         <v>1045.852101855365</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.8</v>
+        <v>-9.69</v>
       </c>
       <c r="L12" t="n">
-        <v>9.15</v>
+        <v>10.04</v>
       </c>
       <c r="M12" t="n">
         <v>0.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.45</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H13" t="n">
-        <v>881.55</v>
+        <v>896</v>
       </c>
       <c r="I13" t="n">
         <v>885.2906861736626</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>14.33</v>
+        <v>12.92</v>
       </c>
       <c r="L13" t="n">
         <v>3.69</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44599</v>
+        <v>44600</v>
       </c>
       <c r="H14" t="n">
-        <v>835.05</v>
+        <v>819.35</v>
       </c>
       <c r="I14" t="n">
         <v>822.3148488142643</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.8</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>7.17</v>
+        <v>8.93</v>
       </c>
       <c r="M14" t="n">
         <v>0.18</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.25</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H15" t="n">
-        <v>806.3</v>
+        <v>816.7</v>
       </c>
       <c r="I15" t="n">
         <v>812.0761960389675</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>1.59</v>
+        <v>0.32</v>
       </c>
       <c r="L15" t="n">
         <v>6.56</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.75</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H16" t="n">
-        <v>811</v>
+        <v>794.45</v>
       </c>
       <c r="I16" t="n">
         <v>804.2789692244401</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7</v>
+        <v>-2.72</v>
       </c>
       <c r="L16" t="n">
-        <v>1.76</v>
+        <v>4.13</v>
       </c>
       <c r="M16" t="n">
         <v>1.96</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.04</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H17" t="n">
-        <v>731.85</v>
+        <v>760</v>
       </c>
       <c r="I17" t="n">
         <v>749.3970725364445</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" t="n">
-        <v>7.88</v>
+        <v>4.34</v>
       </c>
       <c r="L17" t="n">
         <v>6.7</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.07</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44792</v>
+        <v>44795</v>
       </c>
       <c r="H18" t="n">
-        <v>921</v>
+        <v>903.65</v>
       </c>
       <c r="I18" t="n">
         <v>915.8389294698006</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K18" t="n">
-        <v>21.18</v>
+        <v>18.9</v>
       </c>
       <c r="L18" t="n">
         <v>2.89</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.37</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44993</v>
+        <v>44994</v>
       </c>
       <c r="H19" t="n">
-        <v>750.15</v>
+        <v>767.1</v>
       </c>
       <c r="I19" t="n">
         <v>764.4453277306947</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K19" t="n">
-        <v>16.99</v>
+        <v>15.11</v>
       </c>
       <c r="L19" t="n">
         <v>8.73</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>6.44</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H20" t="n">
-        <v>723.95</v>
+        <v>710.6</v>
       </c>
       <c r="I20" t="n">
         <v>717.7138343005238</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.63</v>
+        <v>-7.37</v>
       </c>
       <c r="L20" t="n">
-        <v>6.13</v>
+        <v>7.63</v>
       </c>
       <c r="M20" t="n">
         <v>0.93</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.37</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H21" t="n">
-        <v>758.75</v>
+        <v>762.15</v>
       </c>
       <c r="I21" t="n">
         <v>760.9812172435547</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.78</v>
+        <v>-7.25</v>
       </c>
       <c r="L21" t="n">
-        <v>7.09</v>
+        <v>8.06</v>
       </c>
       <c r="M21" t="n">
         <v>1.25</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H22" t="n">
-        <v>880.3</v>
+        <v>857.1</v>
       </c>
       <c r="I22" t="n">
         <v>879.3189001597639</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
-        <v>15.5</v>
+        <v>12.46</v>
       </c>
       <c r="L22" t="n">
         <v>1.85</v>
@@ -1695,7 +1958,7 @@
         <v>0.58</v>
       </c>
       <c r="N22" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="O22" t="n">
         <v>0.45</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.8</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45275</v>
+        <v>45278</v>
       </c>
       <c r="H23" t="n">
-        <v>776.35</v>
+        <v>781.2</v>
       </c>
       <c r="I23" t="n">
         <v>778.2579229487975</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K23" t="n">
-        <v>9.42</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>4.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.79</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H24" t="n">
-        <v>744.75</v>
+        <v>729.9</v>
       </c>
       <c r="I24" t="n">
         <v>735.9544180054761</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.67</v>
+        <v>-6.57</v>
       </c>
       <c r="L24" t="n">
-        <v>5.46</v>
+        <v>7.39</v>
       </c>
       <c r="M24" t="n">
         <v>0.43</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.69</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H25" t="n">
-        <v>694.15</v>
+        <v>730.35</v>
       </c>
       <c r="I25" t="n">
         <v>726.7112310961024</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9</v>
+        <v>-0.06</v>
       </c>
       <c r="L25" t="n">
         <v>4.53</v>
@@ -1866,7 +2165,7 @@
         <v>1.41</v>
       </c>
       <c r="N25" t="n">
-        <v>2.49</v>
+        <v>5.22</v>
       </c>
       <c r="O25" t="n">
         <v>-1.99</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.34</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H26" t="n">
-        <v>709.85</v>
+        <v>708.05</v>
       </c>
       <c r="I26" t="n">
         <v>708.884564967495</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.81</v>
+        <v>-3.05</v>
       </c>
       <c r="L26" t="n">
         <v>5.1</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.01</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H27" t="n">
-        <v>717.45</v>
+        <v>727.05</v>
       </c>
       <c r="I27" t="n">
         <v>724.7504570808634</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.33</v>
+        <v>-2.68</v>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>3.33</v>
       </c>
       <c r="M27" t="n">
         <v>1.86</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H28" t="n">
-        <v>702.35</v>
+        <v>698.65</v>
       </c>
       <c r="I28" t="n">
         <v>702.0631971724073</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.4</v>
+        <v>-3.91</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="M28" t="n">
         <v>2.59</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45530</v>
+        <v>45531</v>
       </c>
       <c r="H29" t="n">
-        <v>720.35</v>
+        <v>736.75</v>
       </c>
       <c r="I29" t="n">
         <v>733.0071694896385</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.11</v>
+        <v>-5.45</v>
       </c>
       <c r="L29" t="n">
-        <v>3.54</v>
+        <v>5.91</v>
       </c>
       <c r="M29" t="n">
         <v>0.63</v>
       </c>
       <c r="N29" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>-0.53</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H30" t="n">
-        <v>770.2</v>
+        <v>749.75</v>
       </c>
       <c r="I30" t="n">
         <v>760.5450253030629</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K30" t="n">
-        <v>4.54</v>
+        <v>1.76</v>
       </c>
       <c r="L30" t="n">
         <v>2.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
         <v>2.28</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H31" t="n">
-        <v>714.7</v>
+        <v>724.4</v>
       </c>
       <c r="I31" t="n">
         <v>723.6486644012518</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K31" t="n">
-        <v>4.67</v>
+        <v>3.38</v>
       </c>
       <c r="L31" t="n">
         <v>4.03</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.2</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H32" t="n">
-        <v>703.4</v>
+        <v>687</v>
       </c>
       <c r="I32" t="n">
         <v>689.7662113278174</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.9</v>
+        <v>-5.16</v>
       </c>
       <c r="L32" t="n">
-        <v>3.78</v>
+        <v>5.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.48</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="O32" t="n">
         <v>1.36</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.65</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H33" t="n">
-        <v>702.7</v>
+        <v>723.55</v>
       </c>
       <c r="I33" t="n">
         <v>710.3372161923203</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.29</v>
+        <v>-5.32</v>
       </c>
       <c r="L33" t="n">
-        <v>3.08</v>
+        <v>6.07</v>
       </c>
       <c r="M33" t="n">
         <v>0.63</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H34" t="n">
-        <v>848</v>
+        <v>812.05</v>
       </c>
       <c r="I34" t="n">
         <v>815.8071999627929</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>12.23</v>
       </c>
       <c r="L34" t="n">
         <v>3.52</v>
       </c>
       <c r="M34" t="n">
-        <v>4.65</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>2.16</v>
+        <v>4.24</v>
       </c>
       <c r="O34" t="n">
         <v>2.97</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>7.85</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H35" t="n">
-        <v>852</v>
+        <v>882.4</v>
       </c>
       <c r="I35" t="n">
         <v>875.7992081945735</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.92</v>
+        <v>-8.66</v>
       </c>
       <c r="L35" t="n">
-        <v>5.48</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>0.61</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
         <v>4.24</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.36</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H36" t="n">
-        <v>972.6</v>
+        <v>939.7</v>
       </c>
       <c r="I36" t="n">
         <v>940.1675854163719</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K36" t="n">
-        <v>10.22</v>
+        <v>6.49</v>
       </c>
       <c r="L36" t="n">
         <v>3.25</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H37" t="n">
-        <v>819.35</v>
+        <v>854.4</v>
       </c>
       <c r="I37" t="n">
         <v>841.7505014842226</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
-        <v>12.81</v>
+        <v>9.08</v>
       </c>
       <c r="L37" t="n">
         <v>8.01</v>
@@ -2550,7 +2993,7 @@
         <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>2.84</v>
+        <v>4.28</v>
       </c>
       <c r="O37" t="n">
         <v>-3.38</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H38" t="n">
-        <v>885.75</v>
+        <v>878.65</v>
       </c>
       <c r="I38" t="n">
         <v>882.678451861193</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K38" t="n">
-        <v>3.67</v>
+        <v>2.84</v>
       </c>
       <c r="L38" t="n">
         <v>3.68</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>8.77</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H39" t="n">
-        <v>873.5</v>
+        <v>901.55</v>
       </c>
       <c r="I39" t="n">
         <v>896.979870994045</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>0.59</v>
+        <v>-2.61</v>
       </c>
       <c r="L39" t="n">
-        <v>2.74</v>
+        <v>3.16</v>
       </c>
       <c r="M39" t="n">
         <v>0.84</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H40" t="n">
-        <v>838.3</v>
+        <v>811.8</v>
       </c>
       <c r="I40" t="n">
         <v>832.358435110271</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.02</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>7.59</v>
+        <v>10.38</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>1.77</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
         <v>3.21</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H41" t="n">
-        <v>600.9</v>
+        <v>621.65</v>
       </c>
       <c r="I41" t="n">
         <v>613.8240012918858</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K41" t="n">
-        <v>25.98</v>
+        <v>23.42</v>
       </c>
       <c r="L41" t="n">
         <v>3.34</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="H42" t="n">
-        <v>641.75</v>
+        <v>615</v>
       </c>
       <c r="I42" t="n">
         <v>618.0568682423046</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K42" t="n">
-        <v>3.23</v>
+        <v>-1.07</v>
       </c>
       <c r="L42" t="n">
         <v>6.72</v>
@@ -2835,7 +3338,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>3.67</v>
+        <v>4.17</v>
       </c>
       <c r="O42" t="n">
         <v>3.45</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H43" t="n">
-        <v>658.25</v>
+        <v>674.65</v>
       </c>
       <c r="I43" t="n">
         <v>666.6865796675521</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.03</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>8.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>1.31</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>11.07</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H44" t="n">
-        <v>611.2</v>
+        <v>591</v>
       </c>
       <c r="I44" t="n">
         <v>609.6938120589843</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.4</v>
+        <v>-12.4</v>
       </c>
       <c r="L44" t="n">
-        <v>10.07</v>
+        <v>12.47</v>
       </c>
       <c r="M44" t="n">
         <v>1.39</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3009,6 +3548,14 @@
       <c r="Q45" t="n">
         <v>21</v>
       </c>
+      <c r="R45" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5893,7 +6440,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5903,7 +6450,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -5913,7 +6460,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1911</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="8">
@@ -5923,7 +6470,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -5933,7 +6480,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -5943,7 +6490,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133.2</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="11">
@@ -5983,7 +6530,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.1</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -5993,7 +6540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.98</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="16">
@@ -6003,7 +6550,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.09</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17">
@@ -6013,7 +6560,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88.92</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="18">
@@ -6023,7 +6570,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.2</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="19">
@@ -6033,7 +6580,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.48</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
@@ -6043,7 +6590,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.17</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="21">
@@ -6053,7 +6600,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.66</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="22">
@@ -6063,7 +6610,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6073,7 +6620,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -6083,7 +6630,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="25">
@@ -6103,7 +6650,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.22</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="27">
@@ -6123,7 +6670,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
